--- a/public/results/2025/2025 Weekly Stats - Week 2.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB0DF34-9AD5-4642-A9DE-B51119E92B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF9918D-B4D7-6345-A6FB-50CC17FB01BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40040" yWindow="2480" windowWidth="29860" windowHeight="16420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -495,7 +495,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -1010,33 +1010,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1187,7 +1161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1356,16 +1330,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1376,16 +1341,16 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1394,36 +1359,36 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1431,6 +1396,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1440,6 +1417,75 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1458,7 +1504,7 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1485,86 +1531,17 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2037,23 +2014,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -2067,23 +2044,23 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -2933,110 +2910,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="129" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="111" t="s">
+      <c r="B1" s="130"/>
+      <c r="C1" s="135" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="101" t="s">
+      <c r="D1" s="125" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="126"/>
+      <c r="F1" s="125" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="102"/>
-      <c r="H1" s="98" t="s">
+      <c r="G1" s="126"/>
+      <c r="H1" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="113" t="s">
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="117" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="115"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="119"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="107"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="103">
+      <c r="A2" s="131"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="127">
         <v>45782</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="103">
+      <c r="E2" s="128"/>
+      <c r="F2" s="127">
         <v>45789</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="121" t="s">
+      <c r="G2" s="128"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="123" t="s">
+      <c r="J2" s="110" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="127" t="s">
+      <c r="K2" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="121" t="s">
+      <c r="L2" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="125" t="s">
+      <c r="M2" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="116" t="s">
+      <c r="N2" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="O2" s="116" t="s">
+      <c r="O2" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="116" t="s">
+      <c r="P2" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="Q2" s="116" t="s">
+      <c r="Q2" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="116" t="s">
+      <c r="R2" s="120" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="109"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="112"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="136"/>
       <c r="D3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="76" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="100"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="124"/>
-      <c r="K3" s="128"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="117"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="117"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="121"/>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
@@ -3048,34 +3025,33 @@
       <c r="C4" s="41">
         <v>15</v>
       </c>
-      <c r="D4" s="134" t="s">
+      <c r="D4" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="135"/>
-      <c r="F4" s="72">
+      <c r="E4" s="100"/>
+      <c r="F4" s="69">
         <v>42</v>
       </c>
-      <c r="G4" s="76">
+      <c r="G4" s="73">
         <v>27</v>
       </c>
-      <c r="H4" s="57" t="str">
-        <f t="shared" ref="H4:H15" si="0">D4</f>
-        <v>RAIN OUT</v>
-      </c>
-      <c r="I4" s="89">
+      <c r="H4" s="57">
+        <v>42</v>
+      </c>
+      <c r="I4" s="86">
         <v>1</v>
       </c>
-      <c r="J4" s="92"/>
-      <c r="K4" s="76"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="73"/>
       <c r="L4" s="57">
-        <f>E4+G4+J4+K4</f>
+        <f t="shared" ref="L4:L12" si="0">E4+G4+J4+K4</f>
         <v>27</v>
       </c>
-      <c r="M4" s="130">
+      <c r="M4" s="93">
         <f t="shared" ref="M4:M12" si="1">L4/I4</f>
         <v>27</v>
       </c>
-      <c r="N4" s="81"/>
+      <c r="N4" s="78"/>
       <c r="O4" s="61"/>
       <c r="P4" s="61"/>
       <c r="Q4" s="57"/>
@@ -3091,34 +3067,33 @@
       <c r="C5" s="44">
         <v>13</v>
       </c>
-      <c r="D5" s="136"/>
-      <c r="E5" s="137"/>
-      <c r="F5" s="80">
+      <c r="D5" s="101"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="77">
         <v>42</v>
       </c>
-      <c r="G5" s="77">
+      <c r="G5" s="74">
         <v>25</v>
       </c>
       <c r="H5" s="59">
+        <v>42</v>
+      </c>
+      <c r="I5" s="87">
+        <v>1</v>
+      </c>
+      <c r="J5" s="90">
+        <v>1</v>
+      </c>
+      <c r="K5" s="74"/>
+      <c r="L5" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="90">
-        <v>1</v>
-      </c>
-      <c r="J5" s="93">
-        <v>1</v>
-      </c>
-      <c r="K5" s="77"/>
-      <c r="L5" s="59">
-        <f>E5+G5+J5+K5</f>
         <v>26</v>
       </c>
-      <c r="M5" s="131">
+      <c r="M5" s="94">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="N5" s="82"/>
+      <c r="N5" s="79"/>
       <c r="O5" s="62"/>
       <c r="P5" s="62"/>
       <c r="Q5" s="59"/>
@@ -3134,32 +3109,31 @@
       <c r="C6" s="44">
         <v>22</v>
       </c>
-      <c r="D6" s="136"/>
-      <c r="E6" s="137"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="102"/>
       <c r="F6" s="45">
         <v>53</v>
       </c>
-      <c r="G6" s="77">
+      <c r="G6" s="74">
         <v>23</v>
       </c>
       <c r="H6" s="59">
+        <v>53</v>
+      </c>
+      <c r="I6" s="87">
+        <v>1</v>
+      </c>
+      <c r="J6" s="90"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="90">
-        <v>1</v>
-      </c>
-      <c r="J6" s="93"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="59">
-        <f>E6+G6+J6+K6</f>
         <v>23</v>
       </c>
-      <c r="M6" s="131">
+      <c r="M6" s="94">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="N6" s="82"/>
+      <c r="N6" s="79"/>
       <c r="O6" s="62"/>
       <c r="P6" s="62"/>
       <c r="Q6" s="59"/>
@@ -3177,34 +3151,33 @@
       <c r="C7" s="44">
         <v>8</v>
       </c>
-      <c r="D7" s="136"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="88">
+      <c r="D7" s="101"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="85">
         <v>45</v>
       </c>
-      <c r="G7" s="77">
+      <c r="G7" s="74">
         <v>17</v>
       </c>
       <c r="H7" s="59">
+        <v>45</v>
+      </c>
+      <c r="I7" s="87">
+        <v>1</v>
+      </c>
+      <c r="J7" s="90"/>
+      <c r="K7" s="74">
+        <v>1</v>
+      </c>
+      <c r="L7" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="90">
-        <v>1</v>
-      </c>
-      <c r="J7" s="93"/>
-      <c r="K7" s="77">
-        <v>1</v>
-      </c>
-      <c r="L7" s="59">
-        <f>E7+G7+J7+K7</f>
         <v>18</v>
       </c>
-      <c r="M7" s="131">
+      <c r="M7" s="94">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="N7" s="82"/>
+      <c r="N7" s="79"/>
       <c r="O7" s="62"/>
       <c r="P7" s="62"/>
       <c r="Q7" s="59"/>
@@ -3220,32 +3193,31 @@
       <c r="C8" s="44">
         <v>22</v>
       </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="137"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="102"/>
       <c r="F8" s="45">
         <v>59</v>
       </c>
-      <c r="G8" s="77">
+      <c r="G8" s="74">
         <v>17</v>
       </c>
       <c r="H8" s="59">
+        <v>59</v>
+      </c>
+      <c r="I8" s="87">
+        <v>1</v>
+      </c>
+      <c r="J8" s="90"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="90">
-        <v>1</v>
-      </c>
-      <c r="J8" s="93"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="59">
-        <f>E8+G8+J8+K8</f>
         <v>17</v>
       </c>
-      <c r="M8" s="131">
+      <c r="M8" s="94">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="N8" s="87"/>
+      <c r="N8" s="84"/>
       <c r="O8" s="62"/>
       <c r="P8" s="62"/>
       <c r="Q8" s="59"/>
@@ -3261,32 +3233,31 @@
       <c r="C9" s="44">
         <v>8</v>
       </c>
-      <c r="D9" s="136"/>
-      <c r="E9" s="137"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="102"/>
       <c r="F9" s="45">
         <v>46</v>
       </c>
-      <c r="G9" s="77">
+      <c r="G9" s="74">
         <v>16</v>
       </c>
       <c r="H9" s="59">
+        <v>46</v>
+      </c>
+      <c r="I9" s="87">
+        <v>1</v>
+      </c>
+      <c r="J9" s="90"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="90">
-        <v>1</v>
-      </c>
-      <c r="J9" s="93"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="59">
-        <f>E9+G9+J9+K9</f>
         <v>16</v>
       </c>
-      <c r="M9" s="131">
+      <c r="M9" s="94">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="N9" s="83"/>
+      <c r="N9" s="80"/>
       <c r="O9" s="62"/>
       <c r="P9" s="62"/>
       <c r="Q9" s="59"/>
@@ -3302,32 +3273,31 @@
       <c r="C10" s="44">
         <v>17</v>
       </c>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="102"/>
       <c r="F10" s="45">
         <v>55</v>
       </c>
-      <c r="G10" s="77">
+      <c r="G10" s="74">
         <v>16</v>
       </c>
       <c r="H10" s="59">
+        <v>55</v>
+      </c>
+      <c r="I10" s="87">
+        <v>1</v>
+      </c>
+      <c r="J10" s="90"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="90">
-        <v>1</v>
-      </c>
-      <c r="J10" s="93"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="59">
-        <f>E10+G10+J10+K10</f>
         <v>16</v>
       </c>
-      <c r="M10" s="131">
+      <c r="M10" s="94">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="N10" s="86"/>
+      <c r="N10" s="83"/>
       <c r="O10" s="62"/>
       <c r="P10" s="62"/>
       <c r="Q10" s="59"/>
@@ -3343,32 +3313,31 @@
       <c r="C11" s="44">
         <v>18</v>
       </c>
-      <c r="D11" s="136"/>
-      <c r="E11" s="137"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="102"/>
       <c r="F11" s="45">
         <v>56</v>
       </c>
-      <c r="G11" s="77">
+      <c r="G11" s="74">
         <v>16</v>
       </c>
       <c r="H11" s="59">
+        <v>56</v>
+      </c>
+      <c r="I11" s="87">
+        <v>1</v>
+      </c>
+      <c r="J11" s="90"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="90">
-        <v>1</v>
-      </c>
-      <c r="J11" s="93"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="59">
-        <f>E11+G11+J11+K11</f>
         <v>16</v>
       </c>
-      <c r="M11" s="131">
+      <c r="M11" s="94">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="N11" s="83"/>
+      <c r="N11" s="80"/>
       <c r="O11" s="62"/>
       <c r="P11" s="62"/>
       <c r="Q11" s="59"/>
@@ -3384,34 +3353,33 @@
       <c r="C12" s="44">
         <v>21</v>
       </c>
-      <c r="D12" s="136"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="84">
+      <c r="D12" s="101"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="81">
         <v>61</v>
       </c>
-      <c r="G12" s="77">
+      <c r="G12" s="74">
         <v>14</v>
       </c>
       <c r="H12" s="59">
+        <v>61</v>
+      </c>
+      <c r="I12" s="87">
+        <v>1</v>
+      </c>
+      <c r="J12" s="90">
+        <v>1</v>
+      </c>
+      <c r="K12" s="74"/>
+      <c r="L12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="90">
-        <v>1</v>
-      </c>
-      <c r="J12" s="93">
-        <v>1</v>
-      </c>
-      <c r="K12" s="77"/>
-      <c r="L12" s="59">
-        <f>E12+G12+J12+K12</f>
         <v>15</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="94">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="N12" s="82"/>
+      <c r="N12" s="79"/>
       <c r="O12" s="62"/>
       <c r="P12" s="62"/>
       <c r="Q12" s="59"/>
@@ -3427,24 +3395,23 @@
       <c r="C13" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="136"/>
-      <c r="E13" s="137"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="102"/>
       <c r="F13" s="45">
         <v>41</v>
       </c>
-      <c r="G13" s="77"/>
+      <c r="G13" s="74"/>
       <c r="H13" s="59">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="90">
+        <v>41</v>
+      </c>
+      <c r="I13" s="87">
         <v>1</v>
       </c>
-      <c r="J13" s="93"/>
-      <c r="K13" s="77"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="74"/>
       <c r="L13" s="59"/>
-      <c r="M13" s="131"/>
-      <c r="N13" s="83"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="80"/>
       <c r="O13" s="62"/>
       <c r="P13" s="62"/>
       <c r="Q13" s="59"/>
@@ -3460,24 +3427,23 @@
       <c r="C14" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="136"/>
-      <c r="E14" s="137"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="102"/>
       <c r="F14" s="45">
         <v>46</v>
       </c>
-      <c r="G14" s="77"/>
+      <c r="G14" s="74"/>
       <c r="H14" s="59">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="90">
+        <v>46</v>
+      </c>
+      <c r="I14" s="87">
         <v>1</v>
       </c>
       <c r="J14" s="45"/>
-      <c r="K14" s="129"/>
+      <c r="K14" s="92"/>
       <c r="L14" s="59"/>
-      <c r="M14" s="131"/>
-      <c r="N14" s="83"/>
+      <c r="M14" s="94"/>
+      <c r="N14" s="80"/>
       <c r="O14" s="59"/>
       <c r="P14" s="59"/>
       <c r="Q14" s="59"/>
@@ -3493,24 +3459,23 @@
       <c r="C15" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="136"/>
-      <c r="E15" s="137"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="102"/>
       <c r="F15" s="45">
         <v>51</v>
       </c>
-      <c r="G15" s="77"/>
+      <c r="G15" s="74"/>
       <c r="H15" s="59">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="90">
+        <v>51</v>
+      </c>
+      <c r="I15" s="87">
         <v>1</v>
       </c>
-      <c r="J15" s="93"/>
-      <c r="K15" s="77"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="74"/>
       <c r="L15" s="59"/>
-      <c r="M15" s="131"/>
-      <c r="N15" s="83"/>
+      <c r="M15" s="94"/>
+      <c r="N15" s="80"/>
       <c r="O15" s="62"/>
       <c r="P15" s="62"/>
       <c r="Q15" s="59"/>
@@ -3526,17 +3491,17 @@
       <c r="C16" s="44">
         <v>13</v>
       </c>
-      <c r="D16" s="136"/>
-      <c r="E16" s="137"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="102"/>
       <c r="F16" s="46"/>
-      <c r="G16" s="77"/>
+      <c r="G16" s="74"/>
       <c r="H16" s="59"/>
-      <c r="I16" s="90"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="77"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="74"/>
       <c r="L16" s="59"/>
-      <c r="M16" s="131"/>
-      <c r="N16" s="82"/>
+      <c r="M16" s="94"/>
+      <c r="N16" s="79"/>
       <c r="O16" s="62"/>
       <c r="P16" s="62"/>
       <c r="Q16" s="59"/>
@@ -3552,17 +3517,17 @@
       <c r="C17" s="44">
         <v>2</v>
       </c>
-      <c r="D17" s="136"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="77"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="74"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="77"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="74"/>
       <c r="L17" s="59"/>
-      <c r="M17" s="131"/>
-      <c r="N17" s="82"/>
+      <c r="M17" s="94"/>
+      <c r="N17" s="79"/>
       <c r="O17" s="62"/>
       <c r="P17" s="62"/>
       <c r="Q17" s="59"/>
@@ -3578,17 +3543,17 @@
       <c r="C18" s="44">
         <v>15</v>
       </c>
-      <c r="D18" s="136"/>
-      <c r="E18" s="137"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="102"/>
       <c r="F18" s="45"/>
-      <c r="G18" s="77"/>
+      <c r="G18" s="74"/>
       <c r="H18" s="59"/>
-      <c r="I18" s="90"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="77"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="74"/>
       <c r="L18" s="59"/>
-      <c r="M18" s="131"/>
-      <c r="N18" s="83"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="80"/>
       <c r="O18" s="62"/>
       <c r="P18" s="62"/>
       <c r="Q18" s="59"/>
@@ -3604,63 +3569,60 @@
       <c r="C19" s="44">
         <v>11</v>
       </c>
-      <c r="D19" s="136"/>
-      <c r="E19" s="137"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="102"/>
       <c r="F19" s="45"/>
-      <c r="G19" s="77"/>
+      <c r="G19" s="74"/>
       <c r="H19" s="59"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="77"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="74"/>
       <c r="L19" s="59"/>
-      <c r="M19" s="131"/>
-      <c r="N19" s="82"/>
+      <c r="M19" s="94"/>
+      <c r="N19" s="79"/>
       <c r="O19" s="62"/>
       <c r="P19" s="62"/>
       <c r="Q19" s="59"/>
       <c r="R19" s="65"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="75">
+      <c r="C20" s="72">
         <v>15</v>
       </c>
-      <c r="D20" s="138"/>
-      <c r="E20" s="139"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="104"/>
       <c r="F20" s="53"/>
-      <c r="G20" s="78"/>
+      <c r="G20" s="75"/>
       <c r="H20" s="60"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="78"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="75"/>
       <c r="L20" s="60"/>
-      <c r="M20" s="132"/>
-      <c r="N20" s="85"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="82"/>
       <c r="O20" s="63"/>
       <c r="P20" s="63"/>
       <c r="Q20" s="60"/>
       <c r="R20" s="66"/>
     </row>
     <row r="21" spans="1:18" s="52" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="71"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="68" t="e">
-        <f>AVERAGEIF(D4:D20,"&gt;0")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68">
+      <c r="A21" s="137"/>
+      <c r="B21" s="138"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="139"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139">
         <f>AVERAGEIF(F4:F20,"&gt;0")</f>
         <v>49.75</v>
       </c>
-      <c r="G21" s="68"/>
-      <c r="H21" s="69"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="140"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C22" s="49"/>
@@ -3714,6 +3676,16 @@
     <sortCondition ref="B4:B20"/>
   </sortState>
   <mergeCells count="20">
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="P2:P3"/>
     <mergeCell ref="D4:E20"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="I2:I3"/>
@@ -3721,19 +3693,9 @@
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="K2:K3"/>
-    <mergeCell ref="N1:R1"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="P2:P3"/>
     <mergeCell ref="H1:H3"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4880,23 +4842,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -4910,23 +4872,23 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>

--- a/public/results/2025/2025 Weekly Stats - Week 2.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF9918D-B4D7-6345-A6FB-50CC17FB01BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596BC935-3433-0448-98AF-BBBD797523F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40040" yWindow="2480" windowWidth="29860" windowHeight="16420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40040" yWindow="2480" windowWidth="29860" windowHeight="16420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="14" r:id="rId1"/>
@@ -1410,6 +1410,18 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1417,6 +1429,57 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="21" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1471,21 +1534,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1494,54 +1542,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2014,23 +2014,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -2044,23 +2044,23 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -2910,87 +2910,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="135" t="s">
+      <c r="B1" s="104"/>
+      <c r="C1" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="125" t="s">
+      <c r="D1" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="126"/>
-      <c r="F1" s="125" t="s">
+      <c r="E1" s="112"/>
+      <c r="F1" s="111" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="126"/>
-      <c r="H1" s="122" t="s">
+      <c r="G1" s="112"/>
+      <c r="H1" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="117" t="s">
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="119"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="117"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="131"/>
-      <c r="B2" s="132"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="127">
+      <c r="A2" s="105"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="113">
         <v>45782</v>
       </c>
-      <c r="E2" s="128"/>
-      <c r="F2" s="127">
+      <c r="E2" s="114"/>
+      <c r="F2" s="113">
         <v>45789</v>
       </c>
-      <c r="G2" s="128"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="108" t="s">
+      <c r="G2" s="114"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="110" t="s">
+      <c r="J2" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="115" t="s">
+      <c r="K2" s="136" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="108" t="s">
+      <c r="L2" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="113" t="s">
+      <c r="M2" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="120" t="s">
+      <c r="N2" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="O2" s="120" t="s">
+      <c r="O2" s="118" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="120" t="s">
+      <c r="P2" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="Q2" s="120" t="s">
+      <c r="Q2" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="120" t="s">
+      <c r="R2" s="118" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="133"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="136"/>
+      <c r="A3" s="107"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="110"/>
       <c r="D3" s="38" t="s">
         <v>4</v>
       </c>
@@ -3003,17 +3003,17 @@
       <c r="G3" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="124"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="112"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="121"/>
-      <c r="R3" s="121"/>
+      <c r="H3" s="140"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="119"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="Q3" s="119"/>
+      <c r="R3" s="119"/>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
@@ -3025,10 +3025,10 @@
       <c r="C4" s="41">
         <v>15</v>
       </c>
-      <c r="D4" s="99" t="s">
+      <c r="D4" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="100"/>
+      <c r="E4" s="121"/>
       <c r="F4" s="69">
         <v>42</v>
       </c>
@@ -3067,8 +3067,8 @@
       <c r="C5" s="44">
         <v>13</v>
       </c>
-      <c r="D5" s="101"/>
-      <c r="E5" s="102"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="77">
         <v>42</v>
       </c>
@@ -3109,8 +3109,8 @@
       <c r="C6" s="44">
         <v>22</v>
       </c>
-      <c r="D6" s="101"/>
-      <c r="E6" s="102"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="123"/>
       <c r="F6" s="45">
         <v>53</v>
       </c>
@@ -3151,8 +3151,8 @@
       <c r="C7" s="44">
         <v>8</v>
       </c>
-      <c r="D7" s="101"/>
-      <c r="E7" s="102"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123"/>
       <c r="F7" s="85">
         <v>45</v>
       </c>
@@ -3193,8 +3193,8 @@
       <c r="C8" s="44">
         <v>22</v>
       </c>
-      <c r="D8" s="101"/>
-      <c r="E8" s="102"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="123"/>
       <c r="F8" s="45">
         <v>59</v>
       </c>
@@ -3233,8 +3233,8 @@
       <c r="C9" s="44">
         <v>8</v>
       </c>
-      <c r="D9" s="101"/>
-      <c r="E9" s="102"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="123"/>
       <c r="F9" s="45">
         <v>46</v>
       </c>
@@ -3273,8 +3273,8 @@
       <c r="C10" s="44">
         <v>17</v>
       </c>
-      <c r="D10" s="101"/>
-      <c r="E10" s="102"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="123"/>
       <c r="F10" s="45">
         <v>55</v>
       </c>
@@ -3313,8 +3313,8 @@
       <c r="C11" s="44">
         <v>18</v>
       </c>
-      <c r="D11" s="101"/>
-      <c r="E11" s="102"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="123"/>
       <c r="F11" s="45">
         <v>56</v>
       </c>
@@ -3353,8 +3353,8 @@
       <c r="C12" s="44">
         <v>21</v>
       </c>
-      <c r="D12" s="101"/>
-      <c r="E12" s="102"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="123"/>
       <c r="F12" s="81">
         <v>61</v>
       </c>
@@ -3395,8 +3395,8 @@
       <c r="C13" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="101"/>
-      <c r="E13" s="102"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="123"/>
       <c r="F13" s="45">
         <v>41</v>
       </c>
@@ -3427,8 +3427,8 @@
       <c r="C14" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="101"/>
-      <c r="E14" s="102"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="123"/>
       <c r="F14" s="45">
         <v>46</v>
       </c>
@@ -3459,8 +3459,8 @@
       <c r="C15" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="101"/>
-      <c r="E15" s="102"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="123"/>
       <c r="F15" s="45">
         <v>51</v>
       </c>
@@ -3491,8 +3491,8 @@
       <c r="C16" s="44">
         <v>13</v>
       </c>
-      <c r="D16" s="101"/>
-      <c r="E16" s="102"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="123"/>
       <c r="F16" s="46"/>
       <c r="G16" s="74"/>
       <c r="H16" s="59"/>
@@ -3517,8 +3517,8 @@
       <c r="C17" s="44">
         <v>2</v>
       </c>
-      <c r="D17" s="101"/>
-      <c r="E17" s="102"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="123"/>
       <c r="F17" s="68"/>
       <c r="G17" s="74"/>
       <c r="H17" s="59"/>
@@ -3543,8 +3543,8 @@
       <c r="C18" s="44">
         <v>15</v>
       </c>
-      <c r="D18" s="101"/>
-      <c r="E18" s="102"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="123"/>
       <c r="F18" s="45"/>
       <c r="G18" s="74"/>
       <c r="H18" s="59"/>
@@ -3569,8 +3569,8 @@
       <c r="C19" s="44">
         <v>11</v>
       </c>
-      <c r="D19" s="101"/>
-      <c r="E19" s="102"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="123"/>
       <c r="F19" s="45"/>
       <c r="G19" s="74"/>
       <c r="H19" s="59"/>
@@ -3595,8 +3595,8 @@
       <c r="C20" s="72">
         <v>15</v>
       </c>
-      <c r="D20" s="103"/>
-      <c r="E20" s="104"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="125"/>
       <c r="F20" s="53"/>
       <c r="G20" s="75"/>
       <c r="H20" s="60"/>
@@ -3612,17 +3612,17 @@
       <c r="R20" s="66"/>
     </row>
     <row r="21" spans="1:18" s="52" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="137"/>
-      <c r="B21" s="138"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="139"/>
-      <c r="E21" s="139"/>
-      <c r="F21" s="139">
+      <c r="A21" s="96"/>
+      <c r="B21" s="97"/>
+      <c r="C21" s="97"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="98">
         <f>AVERAGEIF(F4:F20,"&gt;0")</f>
         <v>49.75</v>
       </c>
-      <c r="G21" s="139"/>
-      <c r="H21" s="140"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="99"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C22" s="49"/>
@@ -3676,6 +3676,16 @@
     <sortCondition ref="B4:B20"/>
   </sortState>
   <mergeCells count="20">
+    <mergeCell ref="D4:E20"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="F1:G1"/>
@@ -3686,16 +3696,6 @@
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="P2:P3"/>
-    <mergeCell ref="D4:E20"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H1:H3"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4842,23 +4842,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -4872,23 +4872,23 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
